--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,13 +829,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45163.60966179542</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45216</v>
+      </c>
+    </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>
     <row r="7" ht="19.5" customHeight="1" s="22">
       <c r="A7" s="17" t="inlineStr">
@@ -945,7 +941,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="12" t="n">
-        <v>150.75</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="22">
@@ -954,16 +950,6 @@
     <row r="24" ht="18" customHeight="1" s="22">
       <c r="D24" s="5" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="22">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -1006,15 +992,12 @@
         <v>244.506</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="7.5" customHeight="1" s="22">
       <c r="A40" s="8" t="n"/>
     </row>
     <row r="41" ht="9.75" customHeight="1" s="22"/>
     <row r="42" ht="7.5" customHeight="1" s="22"/>
     <row r="43" ht="7.5" customHeight="1" s="22"/>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="16.5" customHeight="1" s="22">
       <c r="A46" t="inlineStr">
         <is>
@@ -1024,9 +1007,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45216</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
     </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>
@@ -1008,10 +1008,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>
@@ -1008,10 +1008,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,9 +829,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45258.54560681683</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="5.25" customHeight="1" s="22"/>
     <row r="7" ht="19.5" customHeight="1" s="22">
       <c r="A7" s="17" t="inlineStr">
@@ -941,7 +945,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="12" t="n">
-        <v>158.3</v>
+        <v>228.5</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="22">
@@ -950,6 +954,16 @@
     <row r="24" ht="18" customHeight="1" s="22">
       <c r="D24" s="5" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="22">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -989,15 +1003,18 @@
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="12" t="n">
-        <v>244.506</v>
-      </c>
-    </row>
+        <v>282.4</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40" ht="7.5" customHeight="1" s="22">
       <c r="A40" s="8" t="n"/>
     </row>
     <row r="41" ht="9.75" customHeight="1" s="22"/>
     <row r="42" ht="7.5" customHeight="1" s="22"/>
     <row r="43" ht="7.5" customHeight="1" s="22"/>
+    <row r="44"/>
+    <row r="45"/>
     <row r="46" ht="16.5" customHeight="1" s="22">
       <c r="A46" t="inlineStr">
         <is>
@@ -1007,9 +1024,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>

--- a/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS/ma/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,13 +829,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45258.54560681683</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>
     <row r="7" ht="19.5" customHeight="1" s="22">
       <c r="A7" s="17" t="inlineStr">
@@ -945,7 +941,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="12" t="n">
-        <v>228.5</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="22">
@@ -954,16 +950,6 @@
     <row r="24" ht="18" customHeight="1" s="22">
       <c r="D24" s="5" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="22">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -1003,18 +989,15 @@
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="12" t="n">
-        <v>282.4</v>
-      </c>
-    </row>
-    <row r="39"/>
+        <v>244.506</v>
+      </c>
+    </row>
     <row r="40" ht="7.5" customHeight="1" s="22">
       <c r="A40" s="8" t="n"/>
     </row>
     <row r="41" ht="9.75" customHeight="1" s="22"/>
     <row r="42" ht="7.5" customHeight="1" s="22"/>
     <row r="43" ht="7.5" customHeight="1" s="22"/>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="16.5" customHeight="1" s="22">
       <c r="A46" t="inlineStr">
         <is>
@@ -1024,11 +1007,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
